--- a/scripts/tests/fixtures/overview/workbook-statement.xlsx
+++ b/scripts/tests/fixtures/overview/workbook-statement.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="181">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -163,7 +163,7 @@
     <t>Deposits</t>
   </si>
   <si>
-    <t>Withdrawals *</t>
+    <t>Withdrawals{{footnote.evolution.withdrawals}}</t>
   </si>
   <si>
     <t>Net flows</t>
@@ -187,243 +187,261 @@
     <t>Realized on sales</t>
   </si>
   <si>
-    <t>Income *</t>
+    <t>Income{{footnote.evolution.income}}</t>
   </si>
   <si>
     <t>Realized total</t>
   </si>
   <si>
-    <t>Fees *</t>
+    <t>Fees{{footnote.evolution.fees}}</t>
+  </si>
+  <si>
+    <t>FX costs{{footnote.evolution.fx_costs}}</t>
+  </si>
+  <si>
+    <t>Costs total</t>
+  </si>
+  <si>
+    <t>Cash movements</t>
+  </si>
+  <si>
+    <t>FX on cash</t>
+  </si>
+  <si>
+    <t>Unexplained</t>
+  </si>
+  <si>
+    <t>Priced</t>
+  </si>
+  <si>
+    <t>Unpriced</t>
+  </si>
+  <si>
+    <t>No rate</t>
+  </si>
+  <si>
+    <t>Missing rate</t>
+  </si>
+  <si>
+    <t>{{table:evolution|period,period_start,period_end,portfolio_id,currency,invested_open,market_value_open,cash_open,unrealized_open,fx_unrealized_open,deposits,withdrawals,flows_net,purchases_at_cost,transfers_in_at_cost,sales_at_cost,transfers_out_at_cost,sales_proceeds,realized_sales,fx_realized,income,realized_total,fees,fx_costs,costs_total,cash_movements,fx_cash,invested_close,market_value_close,cash_close,unrealized_close,fx_unrealized_close,unexplained,priced_instruments,unpriced_instruments,unconverted,missing_rate}}</t>
+  </si>
+  <si>
+    <t>{{table:evolution_notes|note}}</t>
+  </si>
+  <si>
+    <t>{{table:notes_facts|item,value}}</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>{{table:notes_facts_notes|note}}</t>
+  </si>
+  <si>
+    <t>Portfolio statement — Fixture growth (conseq:200900001)</t>
+  </si>
+  <si>
+    <t>Fixture Client · as of 2026-06-15 · 2025-07-01 – 2026-06-15 · in CZK · average cost</t>
+  </si>
+  <si>
+    <t>CZK</t>
+  </si>
+  <si>
+    <t>Total value</t>
+  </si>
+  <si>
+    <t>Invested (average cost)</t>
+  </si>
+  <si>
+    <t>of which exchange rate</t>
+  </si>
+  <si>
+    <t>Withdrawals</t>
+  </si>
+  <si>
+    <t>Net contributions</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Fees and costs</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Plain return</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CZ0008473618</t>
+  </si>
+  <si>
+    <t>Fixture Legacy Fund</t>
+  </si>
+  <si>
+    <t>CZ0008474053</t>
+  </si>
+  <si>
+    <t>Fixture Akcie</t>
+  </si>
+  <si>
+    <t>LU0119195450</t>
+  </si>
+  <si>
+    <t>Fixture Euro Fund</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>security</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>conseq:200900001:RED:1004</t>
+  </si>
+  <si>
+    <t>external-flow</t>
+  </si>
+  <si>
+    <t>withdrawal</t>
+  </si>
+  <si>
+    <t>conseq:200900001:FLOW:DEB:T002</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>transfer-in</t>
+  </si>
+  <si>
+    <t>conseq:200900001:TON:1005</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>buy</t>
+  </si>
+  <si>
+    <t>CZ0003704900</t>
+  </si>
+  <si>
+    <t>conseq:200900001:SUB:1006-rep</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>credit</t>
+  </si>
+  <si>
+    <t>conseq:200900001:CASH:CRE:C001</t>
+  </si>
+  <si>
+    <t>deposit</t>
+  </si>
+  <si>
+    <t>conseq:200900001:FLOW:CRE:T003</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>conseq:200900001:RED:1007</t>
+  </si>
+  <si>
+    <t>debit</t>
+  </si>
+  <si>
+    <t>conseq:200900001:CASH:DEB:C002</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>conseq:200900001:SUB:1008</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>conseq:200900001:SUB:1009</t>
+  </si>
+  <si>
+    <t>reversed by conseq:200900001:SST:1010 (2026-03-03)</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>reversal-of-buy</t>
+  </si>
+  <si>
+    <t>conseq:200900001:SST:1010</t>
+  </si>
+  <si>
+    <t>storno of conseq:200900001:SUB:1009 (2026-02-26)</t>
+  </si>
+  <si>
+    <t>conseq:200900001:RED:1011</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>payout</t>
+  </si>
+  <si>
+    <t>conseq:200900001:PAY:1012</t>
+  </si>
+  <si>
+    <t>transfer-out</t>
+  </si>
+  <si>
+    <t>conseq:200900001:TOFF:1013</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>conseq:200900001:FLOW:CRE:T004</t>
+  </si>
+  <si>
+    <t>conseq:200900001:SUB:1014</t>
+  </si>
+  <si>
+    <t>conseq:200900001:FLOW:DEB:T005</t>
+  </si>
+  <si>
+    <t>conseq:200900001:FLOW:DEB:T006</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>conseq:200900001:SUB:1015</t>
+  </si>
+  <si>
+    <t>Fees</t>
   </si>
   <si>
     <t>FX costs *</t>
   </si>
   <si>
-    <t>Costs total</t>
-  </si>
-  <si>
-    <t>Cash movements</t>
-  </si>
-  <si>
-    <t>FX on cash</t>
-  </si>
-  <si>
-    <t>Unexplained</t>
-  </si>
-  <si>
-    <t>Priced</t>
-  </si>
-  <si>
-    <t>Unpriced</t>
-  </si>
-  <si>
-    <t>No rate</t>
-  </si>
-  <si>
-    <t>Missing rate</t>
-  </si>
-  <si>
-    <t>{{table:evolution|period,period_start,period_end,portfolio_id,currency,invested_open,market_value_open,cash_open,unrealized_open,fx_unrealized_open,deposits,withdrawals,flows_net,purchases_at_cost,transfers_in_at_cost,sales_at_cost,transfers_out_at_cost,sales_proceeds,realized_sales,fx_realized,income,realized_total,fees,fx_costs,costs_total,cash_movements,fx_cash,invested_close,market_value_close,cash_close,unrealized_close,fx_unrealized_close,unexplained,priced_instruments,unpriced_instruments,unconverted,missing_rate}}</t>
-  </si>
-  <si>
-    <t>{{table:evolution_notes|note}}</t>
-  </si>
-  <si>
-    <t>{{table:notes_facts|item,value}}</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>{{table:notes_facts_notes|note}}</t>
-  </si>
-  <si>
-    <t>Portfolio statement — Fixture growth (conseq:200900001)</t>
-  </si>
-  <si>
-    <t>Fixture Client · as of 2026-06-15 · 2025-07-01 – 2026-06-15 · in CZK · average cost</t>
-  </si>
-  <si>
-    <t>CZK</t>
-  </si>
-  <si>
-    <t>Total value</t>
-  </si>
-  <si>
-    <t>Invested (average cost)</t>
-  </si>
-  <si>
-    <t>of which exchange rate</t>
-  </si>
-  <si>
-    <t>Net contributions</t>
-  </si>
-  <si>
-    <t>Fees and costs *</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Plain return</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CZ0008473618</t>
-  </si>
-  <si>
-    <t>Fixture Legacy Fund</t>
-  </si>
-  <si>
-    <t>CZ0008474053</t>
-  </si>
-  <si>
-    <t>Fixture Akcie</t>
-  </si>
-  <si>
-    <t>LU0119195450</t>
-  </si>
-  <si>
-    <t>Fixture Euro Fund</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>2025-07</t>
-  </si>
-  <si>
-    <t>security</t>
-  </si>
-  <si>
-    <t>sell</t>
-  </si>
-  <si>
-    <t>conseq:200900001:RED:1004</t>
-  </si>
-  <si>
-    <t>external-flow</t>
-  </si>
-  <si>
-    <t>withdrawal</t>
-  </si>
-  <si>
-    <t>conseq:200900001:FLOW:DEB:T002</t>
-  </si>
-  <si>
-    <t>2025-09</t>
-  </si>
-  <si>
-    <t>transfer-in</t>
-  </si>
-  <si>
-    <t>conseq:200900001:TON:1005</t>
-  </si>
-  <si>
-    <t>2025-10</t>
-  </si>
-  <si>
-    <t>buy</t>
-  </si>
-  <si>
-    <t>CZ0003704900</t>
-  </si>
-  <si>
-    <t>conseq:200900001:SUB:1006-rep</t>
-  </si>
-  <si>
-    <t>2025-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>credit</t>
-  </si>
-  <si>
-    <t>conseq:200900001:CASH:CRE:C001</t>
-  </si>
-  <si>
-    <t>deposit</t>
-  </si>
-  <si>
-    <t>conseq:200900001:FLOW:CRE:T003</t>
-  </si>
-  <si>
-    <t>2025-12</t>
-  </si>
-  <si>
-    <t>conseq:200900001:RED:1007</t>
-  </si>
-  <si>
-    <t>debit</t>
-  </si>
-  <si>
-    <t>conseq:200900001:CASH:DEB:C002</t>
-  </si>
-  <si>
-    <t>2026-01</t>
-  </si>
-  <si>
-    <t>conseq:200900001:SUB:1008</t>
-  </si>
-  <si>
-    <t>2026-02</t>
-  </si>
-  <si>
-    <t>conseq:200900001:SUB:1009</t>
-  </si>
-  <si>
-    <t>reversed by conseq:200900001:SST:1010 (2026-03-03)</t>
-  </si>
-  <si>
-    <t>2026-03</t>
-  </si>
-  <si>
-    <t>reversal-of-buy</t>
-  </si>
-  <si>
-    <t>conseq:200900001:SST:1010</t>
-  </si>
-  <si>
-    <t>storno of conseq:200900001:SUB:1009 (2026-02-26)</t>
-  </si>
-  <si>
-    <t>conseq:200900001:RED:1011</t>
-  </si>
-  <si>
-    <t>2026-04</t>
-  </si>
-  <si>
-    <t>payout</t>
-  </si>
-  <si>
-    <t>conseq:200900001:PAY:1012</t>
-  </si>
-  <si>
-    <t>transfer-out</t>
-  </si>
-  <si>
-    <t>conseq:200900001:TOFF:1013</t>
-  </si>
-  <si>
-    <t>2026-05</t>
-  </si>
-  <si>
-    <t>conseq:200900001:FLOW:CRE:T004</t>
-  </si>
-  <si>
-    <t>conseq:200900001:SUB:1014</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>conseq:200900001:SUB:1015</t>
-  </si>
-  <si>
     <t>conseq:200900001</t>
   </si>
   <si>
@@ -433,10 +451,10 @@
     <t>2025-08</t>
   </si>
   <si>
-    <t>* withdrawals — Conseq books an entry fee as a withdrawal beside its deposit; it stays inside withdrawals until the model carries each movement's description (IA-C49, IA-P4b).</t>
-  </si>
-  <si>
-    <t>* income, fees, fx_costs — 0: the model carries no fee and no description to tell them by, and none is inferred from an amount (IA-C49, IA-P4b).</t>
+    <t>withdrawals, fees, income — by the provider's label of each movement (income-labels.yaml, named on the Notes): Conseq's entry fees and commissions leave withdrawals for fees; income is what the table classes dividend, coupon or interest. A cash-leg fee or income is shown there too and stays in cash_movements — once: when the external-flow leg carries the same payment (a cash-account contract books a fee on both), the flow counts it.</t>
+  </si>
+  <si>
+    <t>* fx_costs — 0: the model carries no conversion fee, and none is inferred from an amount (IA-C49).</t>
   </si>
   <si>
     <t>fx_unrealized_open, fx_realized and fx_unrealized_close are the exchange-rate parts of the figures beside them — shown, never added to them.</t>
@@ -505,7 +523,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-15T08:00:00Z</t>
+    <t>2026-10-04T19:00:42Z</t>
   </si>
   <si>
     <t>The Summary and the Evolution sheet are investment-evolution:v2's figures for this portfolio, by month, from 2025-07-01 to 2026-06-15.</t>
@@ -514,7 +532,7 @@
     <t>Holdings are what the Evolution's close is valued on: the ledger's units on 2026-06-15, plus any the provider holds that the ledger does not explain, at the latest price on or before that day, converted into CZK at that day's rate; Invested is each holding's cost basis. Cash is the ledger's cash leg on that day. The provider's own valuation may differ by trades still settling.</t>
   </si>
   <si>
-    <t>* Withdrawals hold Conseq's entry fees, and Income and Fees read 0, until the model carries each movement's description (IA-C49, IA-P4b).</t>
+    <t>Withdrawals, Income and Fees follow the provider's label of each movement (income-labels.yaml, named below): Conseq's entry fees and commissions are Fees, not Withdrawals; exchange costs read 0 — the model carries no conversion fee (IA-C49, IA-C55).</t>
   </si>
   <si>
     <t>Transactions are the effective ledger (the substrate's reversal pairs are gone); a Conseq storno is printed with the trade it corrects, and neither reaches the cost basis.</t>
@@ -526,7 +544,10 @@
     <t>Cost basis: average (REPORT_COST_BASIS).</t>
   </si>
   <si>
-    <t>Income and fees: not available: the model carries no `fee`/`description`; fees, income and entry fees read 0, and entry fees stay inside withdrawals (IA-C49).</t>
+    <t>Income and fees: classified by income-labels.yaml v1 (14 labels); 0 of 7 cash and external-flow movements carry a label the table does not know, counted as other; 0 carry no label.</t>
+  </si>
+  <si>
+    <t>Security-leg fees in the window: 1040.00 CZK — the provider's record of the entry fees that arrive as their own withdrawals (classified fee above); not added to fees again.</t>
   </si>
   <si>
     <t>Amounts are in CZK, each converted at its own day's rate from investment.fx_rate (the ČNB fixing via cnb-rates, IA-C68) — the latest rate on or before that day; an amount with no rate is never converted at a guess.</t>
@@ -748,7 +769,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>50000.0</v>
@@ -760,7 +781,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>28900.0</v>
@@ -784,7 +805,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>0.0</v>
@@ -796,10 +817,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.0</v>
+        <v>13515.0</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>75</v>
@@ -808,10 +829,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>26651.67</v>
+        <v>13136.67</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>75</v>
@@ -820,14 +841,14 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>12.882272</v>
+        <v>6.349701</v>
       </c>
     </row>
     <row r="20">
@@ -899,10 +920,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>500.0</v>
@@ -931,10 +952,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>800.0</v>
@@ -963,10 +984,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>90.0</v>
@@ -975,7 +996,7 @@
         <v>10.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>22050.0</v>
@@ -1003,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="12.0"/>
@@ -1065,16 +1086,16 @@
         <v>45853.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>-1200.0</v>
@@ -1086,10 +1107,10 @@
         <v>75</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -1097,16 +1118,16 @@
         <v>45858.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F6" s="10"/>
       <c r="G6" s="9" t="n">
@@ -1116,10 +1137,10 @@
         <v>75</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1127,29 +1148,29 @@
         <v>45905.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>300.0</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -1157,16 +1178,16 @@
         <v>45940.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>100.0</v>
@@ -1178,10 +1199,10 @@
         <v>75</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1189,29 +1210,29 @@
         <v>45964.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="9" t="n">
         <v>2000.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -1219,29 +1240,29 @@
         <v>45964.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="9" t="n">
         <v>2000.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -1249,16 +1270,16 @@
         <v>46001.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>-200.0</v>
@@ -1270,10 +1291,10 @@
         <v>75</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -1281,29 +1302,29 @@
         <v>46006.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="9" t="n">
         <v>500.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -1311,16 +1332,16 @@
         <v>46042.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>50.0</v>
@@ -1332,10 +1353,10 @@
         <v>75</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1343,16 +1364,16 @@
         <v>46079.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>1000.0</v>
@@ -1364,10 +1385,10 @@
         <v>75</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
@@ -1375,16 +1396,16 @@
         <v>46084.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>1000.0</v>
@@ -1396,10 +1417,10 @@
         <v>75</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
@@ -1407,16 +1428,16 @@
         <v>46101.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>-60.0</v>
@@ -1428,10 +1449,10 @@
         <v>75</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -1439,16 +1460,16 @@
         <v>46122.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>100.0</v>
@@ -1460,10 +1481,10 @@
         <v>75</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -1471,29 +1492,29 @@
         <v>46127.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>100.0</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -1501,16 +1522,16 @@
         <v>46147.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="9" t="n">
@@ -1520,10 +1541,10 @@
         <v>75</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -1531,16 +1552,16 @@
         <v>46148.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>200.0</v>
@@ -1552,46 +1573,106 @@
         <v>75</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
+        <v>46150.0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="9" t="n">
+        <v>1040.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>46150.0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="9" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
         <v>46183.0</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="10" t="n">
+      <c r="B23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>100.0</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G23" s="9" t="n">
         <v>13200.0</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4"/>
+      <c r="H23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1635,7 +1716,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>1500.0</v>
@@ -1801,7 +1882,7 @@
         <v>47</v>
       </c>
       <c r="L5" t="s" s="6">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="M5" t="s" s="6">
         <v>49</v>
@@ -1828,16 +1909,16 @@
         <v>46</v>
       </c>
       <c r="U5" t="s" s="6">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="V5" t="s" s="6">
         <v>57</v>
       </c>
       <c r="W5" t="s" s="6">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="X5" t="s" s="6">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="Y5" t="s" s="6">
         <v>60</v>
@@ -1881,7 +1962,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>45839.0</v>
@@ -1890,7 +1971,7 @@
         <v>45869.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>75</v>
@@ -1989,12 +2070,12 @@
         <v>0.0</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>45839.0</v>
@@ -2003,7 +2084,7 @@
         <v>45869.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>75</v>
@@ -2102,12 +2183,12 @@
         <v>0.0</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>45870.0</v>
@@ -2116,7 +2197,7 @@
         <v>45900.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>75</v>
@@ -2215,12 +2296,12 @@
         <v>0.0</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>45870.0</v>
@@ -2229,7 +2310,7 @@
         <v>45900.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>75</v>
@@ -2328,12 +2409,12 @@
         <v>0.0</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>45901.0</v>
@@ -2342,7 +2423,7 @@
         <v>45930.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>75</v>
@@ -2441,12 +2522,12 @@
         <v>0.0</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>45901.0</v>
@@ -2455,7 +2536,7 @@
         <v>45930.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>75</v>
@@ -2554,12 +2635,12 @@
         <v>0.0</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>45931.0</v>
@@ -2568,7 +2649,7 @@
         <v>45961.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>75</v>
@@ -2667,12 +2748,12 @@
         <v>0.0</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>45931.0</v>
@@ -2681,7 +2762,7 @@
         <v>45961.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>75</v>
@@ -2780,12 +2861,12 @@
         <v>0.0</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>45962.0</v>
@@ -2794,7 +2875,7 @@
         <v>45991.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>75</v>
@@ -2893,12 +2974,12 @@
         <v>0.0</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>45962.0</v>
@@ -2907,7 +2988,7 @@
         <v>45991.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>75</v>
@@ -3006,12 +3087,12 @@
         <v>0.0</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>45992.0</v>
@@ -3020,7 +3101,7 @@
         <v>46022.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>75</v>
@@ -3077,13 +3158,13 @@
         <v>2760.0</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="X16" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="Z16" s="9" t="n">
         <v>-12275.0</v>
@@ -3119,12 +3200,12 @@
         <v>0.0</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>45992.0</v>
@@ -3133,7 +3214,7 @@
         <v>46022.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>75</v>
@@ -3190,13 +3271,13 @@
         <v>2760.0</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="X17" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>0.0</v>
+        <v>12275.0</v>
       </c>
       <c r="Z17" s="9" t="n">
         <v>-12275.0</v>
@@ -3232,12 +3313,12 @@
         <v>0.0</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>46023.0</v>
@@ -3246,7 +3327,7 @@
         <v>46053.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>75</v>
@@ -3345,12 +3426,12 @@
         <v>0.0</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>46023.0</v>
@@ -3359,7 +3440,7 @@
         <v>46053.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>75</v>
@@ -3458,12 +3539,12 @@
         <v>0.0</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>46054.0</v>
@@ -3472,7 +3553,7 @@
         <v>46081.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>75</v>
@@ -3571,12 +3652,12 @@
         <v>0.0</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>46054.0</v>
@@ -3585,7 +3666,7 @@
         <v>46081.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>75</v>
@@ -3684,12 +3765,12 @@
         <v>0.0</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>46082.0</v>
@@ -3698,7 +3779,7 @@
         <v>46112.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>75</v>
@@ -3797,12 +3878,12 @@
         <v>0.0</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>46082.0</v>
@@ -3811,7 +3892,7 @@
         <v>46112.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>75</v>
@@ -3910,12 +3991,12 @@
         <v>0.0</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>46113.0</v>
@@ -3924,7 +4005,7 @@
         <v>46142.0</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>75</v>
@@ -4023,12 +4104,12 @@
         <v>0.0</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>46113.0</v>
@@ -4037,7 +4118,7 @@
         <v>46142.0</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>75</v>
@@ -4136,12 +4217,12 @@
         <v>0.0</v>
       </c>
       <c r="AK25" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>46143.0</v>
@@ -4150,7 +4231,7 @@
         <v>46173.0</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>75</v>
@@ -4207,13 +4288,13 @@
         <v>0.0</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="X26" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y26" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="Z26" s="9" t="n">
         <v>0.0</v>
@@ -4249,12 +4330,12 @@
         <v>0.0</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>46143.0</v>
@@ -4263,7 +4344,7 @@
         <v>46173.0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>75</v>
@@ -4320,13 +4401,13 @@
         <v>0.0</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="X27" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>0.0</v>
+        <v>1240.0</v>
       </c>
       <c r="Z27" s="9" t="n">
         <v>0.0</v>
@@ -4362,12 +4443,12 @@
         <v>0.0</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>46174.0</v>
@@ -4376,7 +4457,7 @@
         <v>46188.0</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>75</v>
@@ -4475,12 +4556,12 @@
         <v>0.0</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>46174.0</v>
@@ -4489,7 +4570,7 @@
         <v>46188.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>75</v>
@@ -4588,32 +4669,32 @@
         <v>0.0</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4623,7 +4704,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.0"/>
@@ -4653,7 +4734,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6">
@@ -4661,23 +4742,23 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
@@ -4685,7 +4766,7 @@
         <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -4698,58 +4779,58 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
@@ -4759,57 +4840,62 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
